--- a/bindings/excel/examples/historical_pricing_example.xlsx
+++ b/bindings/excel/examples/historical_pricing_example.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
   <si>
     <t>Market reference date</t>
   </si>
@@ -114,6 +114,18 @@
   </si>
   <si>
     <t>Previous preserves the matched market's valuation date; it does not roll curves to the requested date.</t>
+  </si>
+  <si>
+    <t>Native swap instrument</t>
+  </si>
+  <si>
+    <t>Explicit CSA discount policy</t>
+  </si>
+  <si>
+    <t>Native cashflow pricer</t>
+  </si>
+  <si>
+    <t>Evaluation results</t>
   </si>
   <si>
     <t>2026-01-15</t>
@@ -511,7 +523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="38.7109375" style="1" customWidth="1"/>
@@ -523,10 +535,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -534,10 +546,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -658,12 +670,21 @@
         <v>0</v>
       </c>
     </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="1" cm="1">
+        <f t="array" ref="B16">_xll.QS.INSTRUMENT.SWAP("history_instrument","2026-01-19","2031-01-19","USD","SOFR",1000000,0.04,0,"Actual360","Simple","Semiannual","Semiannual","Quarterly")</f>
+        <v>0</v>
+      </c>
+    </row>
     <row r="17" spans="1:3">
       <c r="A17" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B17" s="1" cm="1">
-        <f t="array" ref="B17">_xll.QS.TRADE.SWAP("history_swap","2026-01-15","2026-01-19","2031-01-19","USD","SOFR",1000000,0.04,0,"Receive","Actual360","Simple","Semiannual","Semiannual","Quarterly")</f>
+        <f t="array" ref="B17">_xll.QS.TRADE.CREATE("history_swap",B16,"2026-01-15","Receive")</f>
         <v>0</v>
       </c>
     </row>
@@ -672,10 +693,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -735,11 +756,11 @@
         <v>20</v>
       </c>
       <c r="B24" s="5" cm="1">
-        <f t="array" ref="B24">_xll.QS.PRICE($B$17,B21)</f>
+        <f t="array" ref="B24">_xll.QS.RESULT.VALUE(B33)</f>
         <v>0</v>
       </c>
       <c r="C24" s="5" cm="1">
-        <f t="array" ref="C24">_xll.QS.PRICE($B$17,C21)</f>
+        <f t="array" ref="C24">_xll.QS.RESULT.VALUE(C33)</f>
         <v>0</v>
       </c>
     </row>
@@ -774,6 +795,37 @@
     <row r="30" spans="1:3">
       <c r="A30" s="1" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B31" s="1" cm="1">
+        <f t="array" ref="B31">_xll.QS.DISCOUNT.POLICY.CSA("history_policy","USD","SOFR")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" s="1" cm="1">
+        <f t="array" ref="B32">_xll.QS.PRICER.CREATE("history_pricer","DiscountedCashflowPricer",B31)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" s="1" cm="1">
+        <f t="array" ref="B33">_xll.QS.EVALUATE("history_result_B",$B$32,$B$17,B21,"Value")</f>
+        <v>0</v>
+      </c>
+      <c r="C33" s="1" cm="1">
+        <f t="array" ref="C33">_xll.QS.EVALUATE("history_result_C",$B$32,$B$17,C21,"Value")</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/bindings/excel/examples/historical_pricing_example.xlsx
+++ b/bindings/excel/examples/historical_pricing_example.xlsx
@@ -2134,7 +2134,7 @@
         <v>90</v>
       </c>
       <c r="B16" s="10" cm="1" t="str">
-        <f t="array" ref="B16">_xll.QS.CONTEXT.CREATE("History.Context1",History_Quotes1,History_Curves1,,,,,,,,,,"USD","SOFR","Mid")</f>
+        <f t="array" ref="B16">_xll.QS.CONTEXT.FROM.COMPONENTS("History.Context1",History_Quotes1,History_Curves1,,,,,,,,,,"USD","SOFR","Mid")</f>
         <v/>
       </c>
       <c r="C16" s="7" t="s">
@@ -2144,7 +2144,7 @@
     <row r="17" spans="1:3" ht="34" customHeight="1">
       <c r="A17" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B16),",",", ")</f>
-        <v>=QS.CONTEXT.CREATE("History.Context1", History_Quotes1, History_Curves1, , , , , , , , , , "USD", "SOFR", "Mid")</v>
+        <v>=QS.CONTEXT.FROM.COMPONENTS("History.Context1", History_Quotes1, History_Curves1, , , , , , , , , , "USD", "SOFR", "Mid")</v>
       </c>
       <c r="B17" s="13"/>
       <c r="C17" s="13"/>
@@ -2234,7 +2234,7 @@
         <v>97</v>
       </c>
       <c r="B31" s="10" cm="1" t="str">
-        <f t="array" ref="B31">_xll.QS.CONTEXT.CREATE("History.Context2",History_Quotes2,History_Curves2,,,,,,,,,,"USD","SOFR","Mid")</f>
+        <f t="array" ref="B31">_xll.QS.CONTEXT.FROM.COMPONENTS("History.Context2",History_Quotes2,History_Curves2,,,,,,,,,,"USD","SOFR","Mid")</f>
         <v/>
       </c>
       <c r="C31" s="7" t="s">
@@ -2244,7 +2244,7 @@
     <row r="32" spans="1:3" ht="34" customHeight="1">
       <c r="A32" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B31),",",", ")</f>
-        <v>=QS.CONTEXT.CREATE("History.Context2", History_Quotes2, History_Curves2, , , , , , , , , , "USD", "SOFR", "Mid")</v>
+        <v>=QS.CONTEXT.FROM.COMPONENTS("History.Context2", History_Quotes2, History_Curves2, , , , , , , , , , "USD", "SOFR", "Mid")</v>
       </c>
       <c r="B32" s="13"/>
       <c r="C32" s="13"/>

--- a/bindings/excel/examples/historical_pricing_example.xlsx
+++ b/bindings/excel/examples/historical_pricing_example.xlsx
@@ -17,23 +17,22 @@
   <definedNames>
     <definedName name="History_ActualDate1">'5 Results'!$B$9</definedName>
     <definedName name="History_ActualDate2">'5 Results'!$C$9</definedName>
-    <definedName name="History_Archive">'3 Archive'!$B$41</definedName>
+    <definedName name="History_Archive">'3 Archive'!$B$35</definedName>
     <definedName name="History_Context1">'4 Pricing'!$B$22</definedName>
     <definedName name="History_Context2">'4 Pricing'!$B$31</definedName>
-    <definedName name="History_Curves1">'3 Archive'!$B$13</definedName>
-    <definedName name="History_Curves2">'3 Archive'!$B$28</definedName>
     <definedName name="History_Date1">'2 Markets'!$B$7</definedName>
     <definedName name="History_Date2">'2 Markets'!$C$7</definedName>
     <definedName name="History_FixedRate">'1 Inputs'!$B$11</definedName>
-    <definedName name="History_InitialCurves1">'3 Archive'!$B$10</definedName>
-    <definedName name="History_InitialCurves2">'3 Archive'!$B$25</definedName>
     <definedName name="History_Instrument">'4 Pricing'!$B$7</definedName>
+    <definedName name="History_MarketInputs1">'3 Archive'!$B$10</definedName>
+    <definedName name="History_MarketInputs2">'3 Archive'!$B$22</definedName>
     <definedName name="History_Matched1">'5 Results'!$B$8</definedName>
     <definedName name="History_Matched2">'5 Results'!$C$8</definedName>
     <definedName name="History_Maturity">'1 Inputs'!$B$9</definedName>
     <definedName name="History_Notional">'1 Inputs'!$B$10</definedName>
-    <definedName name="History_OriginalContext1">'3 Archive'!$B$16</definedName>
-    <definedName name="History_OriginalContext2">'3 Archive'!$B$31</definedName>
+    <definedName name="History_ObservationTimes">'3 Archive'!$D$32:$D$33</definedName>
+    <definedName name="History_OriginalContext1">'3 Archive'!$B$13</definedName>
+    <definedName name="History_OriginalContext2">'3 Archive'!$B$25</definedName>
     <definedName name="History_Pillars">'2 Markets'!$A$12:$A$14</definedName>
     <definedName name="History_Policy">'4 Pricing'!$B$13</definedName>
     <definedName name="History_Pricer">'4 Pricing'!$B$16</definedName>
@@ -41,20 +40,20 @@
     <definedName name="History_PV2">'5 Results'!$C$12</definedName>
     <definedName name="History_Query1">'1 Inputs'!$B$17</definedName>
     <definedName name="History_Query2">'1 Inputs'!$B$18</definedName>
-    <definedName name="History_Quotes1">'3 Archive'!$B$7</definedName>
-    <definedName name="History_Quotes2">'3 Archive'!$B$22</definedName>
     <definedName name="History_Rates1">'2 Markets'!$B$12:$B$14</definedName>
     <definedName name="History_Rates2">'2 Markets'!$C$12:$C$14</definedName>
     <definedName name="History_Result1">'4 Pricing'!$B$25</definedName>
     <definedName name="History_Result2">'4 Pricing'!$B$34</definedName>
+    <definedName name="History_Root1">'3 Archive'!$B$7</definedName>
+    <definedName name="History_Root2">'3 Archive'!$B$19</definedName>
     <definedName name="History_Rule1">'1 Inputs'!$C$17</definedName>
     <definedName name="History_Rule2">'1 Inputs'!$C$18</definedName>
     <definedName name="History_Selector1">'4 Pricing'!$B$19</definedName>
     <definedName name="History_Selector2">'4 Pricing'!$B$28</definedName>
     <definedName name="History_Side">'1 Inputs'!$B$12</definedName>
-    <definedName name="History_Snapshot1">'3 Archive'!$B$19</definedName>
-    <definedName name="History_Snapshot2">'3 Archive'!$B$34</definedName>
-    <definedName name="History_Snapshots">'3 Archive'!$B$38:$B$39</definedName>
+    <definedName name="History_Snapshot1">'3 Archive'!$B$16</definedName>
+    <definedName name="History_Snapshot2">'3 Archive'!$B$28</definedName>
+    <definedName name="History_Snapshots">'3 Archive'!$B$32:$B$33</definedName>
     <definedName name="History_Start">'1 Inputs'!$B$8</definedName>
     <definedName name="History_Timestamp1">'2 Markets'!$B$8</definedName>
     <definedName name="History_Timestamp2">'2 Markets'!$C$8</definedName>
@@ -174,7 +173,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>The quote-store reference date is the valuation date.</t>
+          <t>Each root owns its market date.</t>
         </r>
       </text>
     </comment>
@@ -187,7 +186,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>A separate configuration is used for each recorded market.</t>
+          <t>Separate pillar and rate arrays.</t>
         </r>
       </text>
     </comment>
@@ -200,7 +199,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Use the visible curve from the matching observation.</t>
+          <t>Compose complete market inputs for reuse.</t>
         </r>
       </text>
     </comment>
@@ -213,7 +212,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Rebuild the curve using that market's reference date.</t>
+          <t>Observation timestamp remains separate from market business date.</t>
         </r>
       </text>
     </comment>
@@ -226,7 +225,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Record the complete construction inputs at its observation timestamp.</t>
+          <t>Each root owns its market date.</t>
         </r>
       </text>
     </comment>
@@ -239,7 +238,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>The quote-store reference date is the valuation date.</t>
+          <t>Separate pillar and rate arrays.</t>
         </r>
       </text>
     </comment>
@@ -252,7 +251,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>A separate configuration is used for each recorded market.</t>
+          <t>Compose complete market inputs for reuse.</t>
         </r>
       </text>
     </comment>
@@ -265,11 +264,11 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Use the visible curve from the matching observation.</t>
+          <t>Observation timestamp remains separate from market business date.</t>
         </r>
       </text>
     </comment>
-    <comment ref="B31" authorId="0">
+    <comment ref="B35" authorId="0">
       <text>
         <r>
           <rPr>
@@ -278,33 +277,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Rebuild the curve using that market's reference date.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B34" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Record the complete construction inputs at its observation timestamp.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B41" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>The archive consumes both captured snapshots.</t>
+          <t>Prepared contexts and their observation timestamps are independent arrays.</t>
         </r>
       </text>
     </comment>
@@ -475,7 +448,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="130">
   <si>
     <t>Historical pricing · follow the timestamps</t>
   </si>
@@ -729,49 +702,40 @@
     <t>Purpose</t>
   </si>
   <si>
-    <t>1.1 Create dated quote store</t>
-  </si>
-  <si>
-    <t>The quote-store reference date is the valuation date.</t>
-  </si>
-  <si>
-    <t>1.2 Create configurations</t>
-  </si>
-  <si>
-    <t>A separate configuration is used for each recorded market.</t>
-  </si>
-  <si>
-    <t>1.3 Configure dated zero curve</t>
-  </si>
-  <si>
-    <t>Use the visible curve from the matching observation.</t>
-  </si>
-  <si>
-    <t>1.4 Initialize dated market</t>
-  </si>
-  <si>
-    <t>Rebuild the curve using that market's reference date.</t>
-  </si>
-  <si>
-    <t>1.5 Capture market snapshot</t>
-  </si>
-  <si>
-    <t>Record the complete construction inputs at its observation timestamp.</t>
-  </si>
-  <si>
-    <t>2.1 Create dated quote store</t>
-  </si>
-  <si>
-    <t>2.2 Create configurations</t>
-  </si>
-  <si>
-    <t>2.3 Configure dated zero curve</t>
-  </si>
-  <si>
-    <t>2.4 Initialize dated market</t>
-  </si>
-  <si>
-    <t>2.5 Capture market snapshot</t>
+    <t>1.1 Create dated context</t>
+  </si>
+  <si>
+    <t>Each root owns its market date.</t>
+  </si>
+  <si>
+    <t>1.2 Add zero curve</t>
+  </si>
+  <si>
+    <t>Separate pillar and rate arrays.</t>
+  </si>
+  <si>
+    <t>1.3 Prepare complete context</t>
+  </si>
+  <si>
+    <t>Compose complete market inputs for reuse.</t>
+  </si>
+  <si>
+    <t>1.4 Capture market</t>
+  </si>
+  <si>
+    <t>Observation timestamp remains separate from market business date.</t>
+  </si>
+  <si>
+    <t>2.1 Create dated context</t>
+  </si>
+  <si>
+    <t>2.2 Add zero curve</t>
+  </si>
+  <si>
+    <t>2.3 Prepare complete context</t>
+  </si>
+  <si>
+    <t>2.4 Capture market</t>
   </si>
   <si>
     <t>Captured snapshot</t>
@@ -786,7 +750,7 @@
     <t>3. Collect snapshot archive</t>
   </si>
   <si>
-    <t>The archive consumes both captured snapshots.</t>
+    <t>Prepared contexts and their observation timestamps are independent arrays.</t>
   </si>
   <si>
     <t>Reprice one trade against selected markets</t>
@@ -2024,7 +1988,7 @@
     <tabColor rgb="FF78909C"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="34.7109375" style="1" customWidth="1"/>
@@ -2074,7 +2038,7 @@
         <v>84</v>
       </c>
       <c r="B7" s="10" cm="1" t="str">
-        <f t="array" ref="B7">_xll.QS.QUOTES.CREATE("History.Quotes1",History_Date1)</f>
+        <f t="array" ref="B7">_xll.QS.CONTEXT.CREATE("History.Root1",History_Date1,"USD","SOFR")</f>
         <v/>
       </c>
       <c r="C7" s="7" t="s">
@@ -2084,7 +2048,7 @@
     <row r="8" spans="1:3" ht="34" customHeight="1">
       <c r="A8" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B7),",",", ")</f>
-        <v>=QS.QUOTES.CREATE("History.Quotes1", History_Date1)</v>
+        <v>=QS.CONTEXT.CREATE("History.Root1", History_Date1, "USD", "SOFR")</v>
       </c>
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
@@ -2094,7 +2058,7 @@
         <v>86</v>
       </c>
       <c r="B10" s="10" cm="1" t="str">
-        <f t="array" ref="B10">_xll.QS.CURVE.CONFIGS.CREATE("History.Curves1")</f>
+        <f t="array" ref="B10">_xll.QS.CONTEXT.ADD.ZERO.CURVE(History_Root1,"SOFR",History_Pillars,History_Rates1,"Actual365","Linear",FALSE,"Continuous","Annual")</f>
         <v/>
       </c>
       <c r="C10" s="7" t="s">
@@ -2104,7 +2068,7 @@
     <row r="11" spans="1:3" ht="34" customHeight="1">
       <c r="A11" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B10),",",", ")</f>
-        <v>=QS.CURVE.CONFIGS.CREATE("History.Curves1")</v>
+        <v>=QS.CONTEXT.ADD.ZERO.CURVE(History_Root1, "SOFR", History_Pillars, History_Rates1, "Actual365", "Linear", FALSE, "Continuous", "Annual")</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -2114,7 +2078,7 @@
         <v>88</v>
       </c>
       <c r="B13" s="10" cm="1" t="str">
-        <f t="array" ref="B13">_xll.QS.CURVE.CONFIGS.ADD.ZERO(History_InitialCurves1,"SOFR","Actual365","Linear",FALSE,History_Pillars,History_Rates1,"Continuous","Annual")</f>
+        <f t="array" ref="B13">_xll.QS.CONTEXT.PREPARE("History.Context1",History_Root1,History_MarketInputs1)</f>
         <v/>
       </c>
       <c r="C13" s="7" t="s">
@@ -2124,7 +2088,7 @@
     <row r="14" spans="1:3" ht="34" customHeight="1">
       <c r="A14" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B13),",",", ")</f>
-        <v>=QS.CURVE.CONFIGS.ADD.ZERO(History_InitialCurves1, "SOFR", "Actual365", "Linear", FALSE, History_Pillars, History_Rates1, "Continuous", "Annual")</v>
+        <v>=QS.CONTEXT.PREPARE("History.Context1", History_Root1, History_MarketInputs1)</v>
       </c>
       <c r="B14" s="13"/>
       <c r="C14" s="13"/>
@@ -2134,190 +2098,158 @@
         <v>90</v>
       </c>
       <c r="B16" s="10" cm="1" t="str">
-        <f t="array" ref="B16">_xll.QS.CONTEXT.FROM.COMPONENTS("History.Context1",History_Quotes1,History_Curves1,,,,,,,,,,"USD","SOFR","Mid")</f>
+        <f t="array" ref="B16">_xll.QS.SNAPSHOT.FROM.CONTEXT("History.Snapshot1",History_Timestamp1,History_OriginalContext1)</f>
         <v/>
       </c>
       <c r="C16" s="7" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="34" customHeight="1">
+    <row r="17" spans="1:4" ht="34" customHeight="1">
       <c r="A17" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B16),",",", ")</f>
-        <v>=QS.CONTEXT.FROM.COMPONENTS("History.Context1", History_Quotes1, History_Curves1, , , , , , , , , , "USD", "SOFR", "Mid")</v>
+        <v>=QS.SNAPSHOT.FROM.CONTEXT("History.Snapshot1", History_Timestamp1, History_OriginalContext1)</v>
       </c>
       <c r="B17" s="13"/>
       <c r="C17" s="13"/>
     </row>
-    <row r="19" spans="1:3" ht="38" customHeight="1">
+    <row r="19" spans="1:4" ht="38" customHeight="1">
       <c r="A19" s="4" t="s">
         <v>92</v>
       </c>
       <c r="B19" s="10" cm="1" t="str">
-        <f t="array" ref="B19">_xll.QS.SNAPSHOT.FROM.CONTEXT("History.Snapshot1",History_Timestamp1,History_OriginalContext1)</f>
+        <f t="array" ref="B19">_xll.QS.CONTEXT.CREATE("History.Root2",History_Date2,"USD","SOFR")</f>
         <v/>
       </c>
       <c r="C19" s="7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="34" customHeight="1">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="34" customHeight="1">
       <c r="A20" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B19),",",", ")</f>
-        <v>=QS.SNAPSHOT.FROM.CONTEXT("History.Snapshot1", History_Timestamp1, History_OriginalContext1)</v>
+        <v>=QS.CONTEXT.CREATE("History.Root2", History_Date2, "USD", "SOFR")</v>
       </c>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
     </row>
-    <row r="22" spans="1:3" ht="38" customHeight="1">
+    <row r="22" spans="1:4" ht="38" customHeight="1">
       <c r="A22" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B22" s="10" cm="1" t="str">
-        <f t="array" ref="B22">_xll.QS.QUOTES.CREATE("History.Quotes2",History_Date2)</f>
+        <f t="array" ref="B22">_xll.QS.CONTEXT.ADD.ZERO.CURVE(History_Root2,"SOFR",History_Pillars,History_Rates2,"Actual365","Linear",FALSE,"Continuous","Annual")</f>
         <v/>
       </c>
       <c r="C22" s="7" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="34" customHeight="1">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="34" customHeight="1">
       <c r="A23" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B22),",",", ")</f>
-        <v>=QS.QUOTES.CREATE("History.Quotes2", History_Date2)</v>
+        <v>=QS.CONTEXT.ADD.ZERO.CURVE(History_Root2, "SOFR", History_Pillars, History_Rates2, "Actual365", "Linear", FALSE, "Continuous", "Annual")</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
     </row>
-    <row r="25" spans="1:3" ht="38" customHeight="1">
+    <row r="25" spans="1:4" ht="38" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B25" s="10" cm="1" t="str">
-        <f t="array" ref="B25">_xll.QS.CURVE.CONFIGS.CREATE("History.Curves2")</f>
+        <f t="array" ref="B25">_xll.QS.CONTEXT.PREPARE("History.Context2",History_Root2,History_MarketInputs2)</f>
         <v/>
       </c>
       <c r="C25" s="7" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="34" customHeight="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="34" customHeight="1">
       <c r="A26" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B25),",",", ")</f>
-        <v>=QS.CURVE.CONFIGS.CREATE("History.Curves2")</v>
+        <v>=QS.CONTEXT.PREPARE("History.Context2", History_Root2, History_MarketInputs2)</v>
       </c>
       <c r="B26" s="13"/>
       <c r="C26" s="13"/>
     </row>
-    <row r="28" spans="1:3" ht="38" customHeight="1">
+    <row r="28" spans="1:4" ht="38" customHeight="1">
       <c r="A28" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B28" s="10" cm="1" t="str">
-        <f t="array" ref="B28">_xll.QS.CURVE.CONFIGS.ADD.ZERO(History_InitialCurves2,"SOFR","Actual365","Linear",FALSE,History_Pillars,History_Rates2,"Continuous","Annual")</f>
+        <f t="array" ref="B28">_xll.QS.SNAPSHOT.FROM.CONTEXT("History.Snapshot2",History_Timestamp2,History_OriginalContext2)</f>
         <v/>
       </c>
       <c r="C28" s="7" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="34" customHeight="1">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="34" customHeight="1">
       <c r="A29" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B28),",",", ")</f>
-        <v>=QS.CURVE.CONFIGS.ADD.ZERO(History_InitialCurves2, "SOFR", "Actual365", "Linear", FALSE, History_Pillars, History_Rates2, "Continuous", "Annual")</v>
+        <v>=QS.SNAPSHOT.FROM.CONTEXT("History.Snapshot2", History_Timestamp2, History_OriginalContext2)</v>
       </c>
       <c r="B29" s="13"/>
       <c r="C29" s="13"/>
     </row>
-    <row r="31" spans="1:3" ht="38" customHeight="1">
-      <c r="A31" s="4" t="s">
+    <row r="31" spans="1:4" ht="36" customHeight="1">
+      <c r="A31" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C31" s="5"/>
+    </row>
+    <row r="32" spans="1:4" ht="24" customHeight="1">
+      <c r="A32" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B31" s="10" cm="1" t="str">
-        <f t="array" ref="B31">_xll.QS.CONTEXT.FROM.COMPONENTS("History.Context2",History_Quotes2,History_Curves2,,,,,,,,,,"USD","SOFR","Mid")</f>
-        <v/>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="34" customHeight="1">
-      <c r="A32" s="13" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B31),",",", ")</f>
-        <v>=QS.CONTEXT.FROM.COMPONENTS("History.Context2", History_Quotes2, History_Curves2, , , , , , , , , , "USD", "SOFR", "Mid")</v>
-      </c>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
-    </row>
-    <row r="34" spans="1:3" ht="38" customHeight="1">
-      <c r="A34" s="4" t="s">
+      <c r="B32" s="10">
+        <f>History_OriginalContext1</f>
+        <v/>
+      </c>
+      <c r="D32" s="8">
+        <f>History_Timestamp1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="24" customHeight="1">
+      <c r="A33" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B34" s="10" cm="1" t="str">
-        <f t="array" ref="B34">_xll.QS.SNAPSHOT.FROM.CONTEXT("History.Snapshot2",History_Timestamp2,History_OriginalContext2)</f>
-        <v/>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="34" customHeight="1">
-      <c r="A35" s="13" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B34),",",", ")</f>
-        <v>=QS.SNAPSHOT.FROM.CONTEXT("History.Snapshot2", History_Timestamp2, History_OriginalContext2)</v>
-      </c>
-      <c r="B35" s="13"/>
-      <c r="C35" s="13"/>
-    </row>
-    <row r="37" spans="1:3" ht="36" customHeight="1">
-      <c r="A37" s="5" t="s">
+      <c r="B33" s="10">
+        <f>History_OriginalContext2</f>
+        <v/>
+      </c>
+      <c r="D33" s="8">
+        <f>History_Timestamp2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="38" customHeight="1">
+      <c r="A35" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C37" s="5"/>
-    </row>
-    <row r="38" spans="1:3" ht="24" customHeight="1">
-      <c r="A38" s="1" t="s">
+      <c r="B35" s="10" cm="1" t="str">
+        <f t="array" ref="B35">_xll.QS.SNAPSHOT.FROM.RANGE("History.Archive",History_Snapshots,History_ObservationTimes)</f>
+        <v/>
+      </c>
+      <c r="C35" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="B38" s="10">
-        <f>History_Snapshot1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="24" customHeight="1">
-      <c r="A39" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B39" s="10">
-        <f>History_Snapshot2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="38" customHeight="1">
-      <c r="A41" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B41" s="10" cm="1" t="str">
-        <f t="array" ref="B41">_xll.QS.SNAPSHOTS.CREATE("History.Archive",History_Snapshots)</f>
-        <v/>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="34" customHeight="1">
-      <c r="A42" s="13" t="str">
-        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B41),",",", ")</f>
-        <v>=QS.SNAPSHOTS.CREATE("History.Archive", History_Snapshots)</v>
-      </c>
-      <c r="B42" s="13"/>
-      <c r="C42" s="13"/>
+    </row>
+    <row r="36" spans="1:4" ht="34" customHeight="1">
+      <c r="A36" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B35),",",", ")</f>
+        <v>=QS.SNAPSHOT.FROM.RANGE("History.Archive", History_Snapshots, History_ObservationTimes)</v>
+      </c>
+      <c r="B36" s="13"/>
+      <c r="C36" s="13"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="11">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C3"/>
     <mergeCell ref="A8:C8"/>
@@ -2328,9 +2260,7 @@
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A36:C36"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" location="'Start Here'!A1" display="← Start Here"/>
@@ -2360,14 +2290,14 @@
   <sheetData>
     <row r="1" spans="1:3" ht="38" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
     </row>
     <row r="2" spans="1:3" ht="24" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -2382,7 +2312,7 @@
         <v>33</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="36" customHeight="1">
@@ -2398,14 +2328,14 @@
     </row>
     <row r="7" spans="1:3" ht="38" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B7" s="10" cm="1" t="str">
         <f t="array" ref="B7">_xll.QS.INSTRUMENT.SWAP("History.Instrument",History_Start,History_Maturity,"USD","SOFR",History_Notional,History_FixedRate,0,"Actual360","Simple","Semiannual","Semiannual","Quarterly")</f>
         <v/>
       </c>
       <c r="C7" s="7" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="48" customHeight="1">
@@ -2418,14 +2348,14 @@
     </row>
     <row r="10" spans="1:3" ht="38" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B10" s="10" cm="1" t="str">
         <f t="array" ref="B10">_xll.QS.TRADE.CREATE("History.Trade",History_Instrument,History_TradeDate,History_Side)</f>
         <v/>
       </c>
       <c r="C10" s="7" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="34" customHeight="1">
@@ -2438,14 +2368,14 @@
     </row>
     <row r="13" spans="1:3" ht="38" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B13" s="10" cm="1" t="str">
         <f t="array" ref="B13">_xll.QS.DISCOUNT.POLICY.CSA("History.Policy","USD","SOFR")</f>
         <v/>
       </c>
       <c r="C13" s="7" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="34" customHeight="1">
@@ -2458,14 +2388,14 @@
     </row>
     <row r="16" spans="1:3" ht="38" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B16" s="10" cm="1" t="str">
         <f t="array" ref="B16">_xll.QS.PRICER.CREATE("History.Pricer","DiscountedCashflowPricer",History_Policy)</f>
         <v/>
       </c>
       <c r="C16" s="7" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="34" customHeight="1">
@@ -2478,14 +2408,14 @@
     </row>
     <row r="19" spans="1:3" ht="38" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B19" s="10" cm="1" t="str">
         <f t="array" ref="B19">_xll.QS.SNAPSHOT.SELECTOR("History.Selector1",History_Query1,History_Rule1,"Mid")</f>
         <v/>
       </c>
       <c r="C19" s="7" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="34" customHeight="1">
@@ -2498,14 +2428,14 @@
     </row>
     <row r="22" spans="1:3" ht="38" customHeight="1">
       <c r="A22" s="4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B22" s="10" cm="1" t="str">
         <f t="array" ref="B22">_xll.QS.CONTEXT.FROM.SNAPSHOT("History.Selected1",History_Archive,History_Selector1)</f>
         <v/>
       </c>
       <c r="C22" s="7" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="34" customHeight="1">
@@ -2518,34 +2448,34 @@
     </row>
     <row r="25" spans="1:3" ht="38" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B25" s="10" cm="1" t="str">
-        <f t="array" ref="B25">_xll.QS.EVALUATE("History.Result1",History_Pricer,History_Trade,History_Context1,"Value")</f>
+        <f t="array" ref="B25">_xll.QS.EVALUATE.RESULTS(History_Context1,History_Trade,"Value",,History_Pricer)</f>
         <v/>
       </c>
       <c r="C25" s="7" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="34" customHeight="1">
       <c r="A26" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B25),",",", ")</f>
-        <v>=QS.EVALUATE("History.Result1", History_Pricer, History_Trade, History_Context1, "Value")</v>
+        <v>=QS.EVALUATE.RESULTS(History_Context1, History_Trade, "Value", , History_Pricer)</v>
       </c>
       <c r="B26" s="13"/>
       <c r="C26" s="13"/>
     </row>
     <row r="28" spans="1:3" ht="38" customHeight="1">
       <c r="A28" s="4" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B28" s="10" cm="1" t="str">
         <f t="array" ref="B28">_xll.QS.SNAPSHOT.SELECTOR("History.Selector2",History_Query2,History_Rule2,"Mid")</f>
         <v/>
       </c>
       <c r="C28" s="7" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="34" customHeight="1">
@@ -2558,14 +2488,14 @@
     </row>
     <row r="31" spans="1:3" ht="38" customHeight="1">
       <c r="A31" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B31" s="10" cm="1" t="str">
         <f t="array" ref="B31">_xll.QS.CONTEXT.FROM.SNAPSHOT("History.Selected2",History_Archive,History_Selector2)</f>
         <v/>
       </c>
       <c r="C31" s="7" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="34" customHeight="1">
@@ -2578,20 +2508,20 @@
     </row>
     <row r="34" spans="1:3" ht="38" customHeight="1">
       <c r="A34" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B34" s="10" cm="1" t="str">
-        <f t="array" ref="B34">_xll.QS.EVALUATE("History.Result2",History_Pricer,History_Trade,History_Context2,"Value")</f>
+        <f t="array" ref="B34">_xll.QS.EVALUATE.RESULTS(History_Context2,History_Trade,"Value",,History_Pricer)</f>
         <v/>
       </c>
       <c r="C34" s="7" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="34" customHeight="1">
       <c r="A35" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B34),",",", ")</f>
-        <v>=QS.EVALUATE("History.Result2", History_Pricer, History_Trade, History_Context2, "Value")</v>
+        <v>=QS.EVALUATE.RESULTS(History_Context2, History_Trade, "Value", , History_Pricer)</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -2639,14 +2569,14 @@
   <sheetData>
     <row r="1" spans="1:3" ht="38" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
     </row>
     <row r="2" spans="1:3" ht="24" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -2663,7 +2593,7 @@
     </row>
     <row r="6" spans="1:3" ht="36" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>57</v>
@@ -2674,7 +2604,7 @@
     </row>
     <row r="7" spans="1:3" ht="36" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B7" s="9">
         <f>History_Query1</f>
@@ -2687,7 +2617,7 @@
     </row>
     <row r="8" spans="1:3" ht="36" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B8" s="9" cm="1" t="str">
         <f t="array" ref="B8">_xll.QS.CONTEXT.SNAPSHOT.TIMESTAMP(History_Context1)</f>
@@ -2700,7 +2630,7 @@
     </row>
     <row r="9" spans="1:3" ht="36" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B9" s="9" cm="1" t="str">
         <f t="array" ref="B9">_xll.QS.CONTEXT.EVALUATION.DATE(History_Context1)</f>
@@ -2726,7 +2656,7 @@
     </row>
     <row r="12" spans="1:3" ht="36" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B12" s="14" cm="1" t="str">
         <f t="array" ref="B12">_xll.QS.RESULT.VALUE(History_Result1)</f>
@@ -2739,7 +2669,7 @@
     </row>
     <row r="13" spans="1:3" ht="36" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B13" s="14">
         <f>History_PV1-History_PV1</f>
@@ -2752,7 +2682,7 @@
     </row>
     <row r="17" spans="1:1" ht="24" customHeight="1">
       <c r="A17" s="6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/bindings/excel/examples/historical_pricing_example.xlsx
+++ b/bindings/excel/examples/historical_pricing_example.xlsx
@@ -1365,7 +1365,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F28"/>
-  <sheetFormatPr defaultRowHeight="26" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="26.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="22.7109375" style="1" customWidth="1"/>
@@ -1392,7 +1392,7 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="1:6" ht="26" customHeight="1">
+    <row r="3" spans="1:6" ht="26.25" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -1402,7 +1402,7 @@
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
     </row>
-    <row r="4" spans="1:6" ht="26" customHeight="1">
+    <row r="4" spans="1:6" ht="26.25" customHeight="1">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -1410,7 +1410,7 @@
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
     </row>
-    <row r="6" spans="1:6" ht="26" customHeight="1">
+    <row r="6" spans="1:6" ht="26.25" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>2</v>
       </c>
@@ -1420,7 +1420,7 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:6" ht="26" customHeight="1">
+    <row r="7" spans="1:6" ht="26.25" customHeight="1">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -1428,7 +1428,7 @@
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="9" spans="1:6" ht="26" customHeight="1">
+    <row r="9" spans="1:6" ht="26.25" customHeight="1">
       <c r="A9" s="5" t="s">
         <v>3</v>
       </c>
@@ -1438,7 +1438,7 @@
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
     </row>
-    <row r="10" spans="1:6" ht="34" customHeight="1">
+    <row r="10" spans="1:6" ht="33.75" customHeight="1">
       <c r="A10" s="4" t="s">
         <v>4</v>
       </c>
@@ -1452,7 +1452,7 @@
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
     </row>
-    <row r="11" spans="1:6" ht="34" customHeight="1">
+    <row r="11" spans="1:6" ht="33.75" customHeight="1">
       <c r="A11" s="4" t="s">
         <v>7</v>
       </c>
@@ -1466,7 +1466,7 @@
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
     </row>
-    <row r="12" spans="1:6" ht="34" customHeight="1">
+    <row r="12" spans="1:6" ht="33.75" customHeight="1">
       <c r="A12" s="4" t="s">
         <v>10</v>
       </c>
@@ -1480,7 +1480,7 @@
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
     </row>
-    <row r="13" spans="1:6" ht="34" customHeight="1">
+    <row r="13" spans="1:6" ht="33.75" customHeight="1">
       <c r="A13" s="4" t="s">
         <v>13</v>
       </c>
@@ -1494,7 +1494,7 @@
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
     </row>
-    <row r="14" spans="1:6" ht="34" customHeight="1">
+    <row r="14" spans="1:6" ht="33.75" customHeight="1">
       <c r="A14" s="4" t="s">
         <v>16</v>
       </c>
@@ -1508,7 +1508,7 @@
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
     </row>
-    <row r="17" spans="1:6" ht="26" customHeight="1">
+    <row r="17" spans="1:6" ht="26.25" customHeight="1">
       <c r="A17" s="5" t="s">
         <v>19</v>
       </c>
@@ -1554,7 +1554,7 @@
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
     </row>
-    <row r="22" spans="1:6" ht="26" customHeight="1">
+    <row r="22" spans="1:6" ht="26.25" customHeight="1">
       <c r="A22" s="5" t="s">
         <v>26</v>
       </c>
@@ -1564,7 +1564,7 @@
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
     </row>
-    <row r="23" spans="1:6" ht="34" customHeight="1">
+    <row r="23" spans="1:6" ht="33.75" customHeight="1">
       <c r="A23" s="1" t="s">
         <v>27</v>
       </c>
@@ -1574,7 +1574,7 @@
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
     </row>
-    <row r="24" spans="1:6" ht="34" customHeight="1">
+    <row r="24" spans="1:6" ht="33.75" customHeight="1">
       <c r="A24" s="1" t="s">
         <v>28</v>
       </c>
@@ -1584,7 +1584,7 @@
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
     </row>
-    <row r="25" spans="1:6" ht="34" customHeight="1">
+    <row r="25" spans="1:6" ht="33.75" customHeight="1">
       <c r="A25" s="1" t="s">
         <v>29</v>
       </c>
@@ -1594,7 +1594,7 @@
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
     </row>
-    <row r="27" spans="1:6" ht="26" customHeight="1">
+    <row r="27" spans="1:6" ht="26.25" customHeight="1">
       <c r="A27" s="7" t="s">
         <v>30</v>
       </c>
@@ -1604,7 +1604,7 @@
       <c r="E27" s="7"/>
       <c r="F27" s="7"/>
     </row>
-    <row r="28" spans="1:6" ht="26" customHeight="1">
+    <row r="28" spans="1:6" ht="26.25" customHeight="1">
       <c r="A28" s="7"/>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
@@ -1667,7 +1667,7 @@
     <col min="3" max="3" width="62.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="38" customHeight="1">
+    <row r="1" spans="1:3" ht="38.25" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>31</v>
       </c>
@@ -1705,7 +1705,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="32" customHeight="1">
+    <row r="7" spans="1:3" ht="32.25" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>38</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="32" customHeight="1">
+    <row r="8" spans="1:3" ht="32.25" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>41</v>
       </c>
@@ -1727,7 +1727,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="32" customHeight="1">
+    <row r="9" spans="1:3" ht="32.25" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>44</v>
       </c>
@@ -1738,7 +1738,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="32" customHeight="1">
+    <row r="10" spans="1:3" ht="32.25" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>47</v>
       </c>
@@ -1749,7 +1749,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="32" customHeight="1">
+    <row r="11" spans="1:3" ht="32.25" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>49</v>
       </c>
@@ -1760,7 +1760,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="32" customHeight="1">
+    <row r="12" spans="1:3" ht="32.25" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>51</v>
       </c>
@@ -1861,7 +1861,7 @@
     <col min="2" max="3" width="30.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="38" customHeight="1">
+    <row r="1" spans="1:3" ht="38.25" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>63</v>
       </c>
@@ -1995,7 +1995,7 @@
     <col min="2" max="3" width="48.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="38" customHeight="1">
+    <row r="1" spans="1:3" ht="38.25" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>78</v>
       </c>
@@ -2033,7 +2033,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="38" customHeight="1">
+    <row r="7" spans="1:3" ht="38.25" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>84</v>
       </c>
@@ -2045,7 +2045,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="34" customHeight="1">
+    <row r="8" spans="1:3" ht="33.75" customHeight="1">
       <c r="A8" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B7),",",", ")</f>
         <v>=QS.CONTEXT.CREATE("History.Root1", History_Date1, "USD", "SOFR")</v>
@@ -2053,27 +2053,27 @@
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
     </row>
-    <row r="10" spans="1:3" ht="38" customHeight="1">
+    <row r="10" spans="1:3" ht="38.25" customHeight="1">
       <c r="A10" s="4" t="s">
         <v>86</v>
       </c>
       <c r="B10" s="10" cm="1" t="str">
-        <f t="array" ref="B10">_xll.QS.CONTEXT.ADD.ZERO.CURVE(History_Root1,"SOFR",History_Pillars,History_Rates1,"Actual365","Linear",FALSE,"Continuous","Annual")</f>
+        <f t="array" ref="B10">_xll.QS.CONTEXT.ADD.ZERO.CURVE(History_Root1,"SOFR",History_Pillars,History_Rates1,"Actual365","Continuous","Annual","Linear",FALSE)</f>
         <v/>
       </c>
       <c r="C10" s="7" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="34" customHeight="1">
+    <row r="11" spans="1:3" ht="33.75" customHeight="1">
       <c r="A11" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B10),",",", ")</f>
-        <v>=QS.CONTEXT.ADD.ZERO.CURVE(History_Root1, "SOFR", History_Pillars, History_Rates1, "Actual365", "Linear", FALSE, "Continuous", "Annual")</v>
+        <v>=QS.CONTEXT.ADD.ZERO.CURVE(History_Root1, "SOFR", History_Pillars, History_Rates1, "Actual365", "Continuous", "Annual", "Linear", FALSE)</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
     </row>
-    <row r="13" spans="1:3" ht="38" customHeight="1">
+    <row r="13" spans="1:3" ht="38.25" customHeight="1">
       <c r="A13" s="4" t="s">
         <v>88</v>
       </c>
@@ -2085,7 +2085,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="34" customHeight="1">
+    <row r="14" spans="1:3" ht="33.75" customHeight="1">
       <c r="A14" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B13),",",", ")</f>
         <v>=QS.CONTEXT.PREPARE("History.Context1", History_Root1, History_MarketInputs1)</v>
@@ -2093,7 +2093,7 @@
       <c r="B14" s="13"/>
       <c r="C14" s="13"/>
     </row>
-    <row r="16" spans="1:3" ht="38" customHeight="1">
+    <row r="16" spans="1:3" ht="38.25" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>90</v>
       </c>
@@ -2105,7 +2105,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="34" customHeight="1">
+    <row r="17" spans="1:4" ht="33.75" customHeight="1">
       <c r="A17" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B16),",",", ")</f>
         <v>=QS.SNAPSHOT.FROM.CONTEXT("History.Snapshot1", History_Timestamp1, History_OriginalContext1)</v>
@@ -2113,7 +2113,7 @@
       <c r="B17" s="13"/>
       <c r="C17" s="13"/>
     </row>
-    <row r="19" spans="1:4" ht="38" customHeight="1">
+    <row r="19" spans="1:4" ht="38.25" customHeight="1">
       <c r="A19" s="4" t="s">
         <v>92</v>
       </c>
@@ -2125,7 +2125,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="34" customHeight="1">
+    <row r="20" spans="1:4" ht="33.75" customHeight="1">
       <c r="A20" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B19),",",", ")</f>
         <v>=QS.CONTEXT.CREATE("History.Root2", History_Date2, "USD", "SOFR")</v>
@@ -2133,27 +2133,27 @@
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
     </row>
-    <row r="22" spans="1:4" ht="38" customHeight="1">
+    <row r="22" spans="1:4" ht="38.25" customHeight="1">
       <c r="A22" s="4" t="s">
         <v>93</v>
       </c>
       <c r="B22" s="10" cm="1" t="str">
-        <f t="array" ref="B22">_xll.QS.CONTEXT.ADD.ZERO.CURVE(History_Root2,"SOFR",History_Pillars,History_Rates2,"Actual365","Linear",FALSE,"Continuous","Annual")</f>
+        <f t="array" ref="B22">_xll.QS.CONTEXT.ADD.ZERO.CURVE(History_Root2,"SOFR",History_Pillars,History_Rates2,"Actual365","Continuous","Annual","Linear",FALSE)</f>
         <v/>
       </c>
       <c r="C22" s="7" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="34" customHeight="1">
+    <row r="23" spans="1:4" ht="33.75" customHeight="1">
       <c r="A23" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B22),",",", ")</f>
-        <v>=QS.CONTEXT.ADD.ZERO.CURVE(History_Root2, "SOFR", History_Pillars, History_Rates2, "Actual365", "Linear", FALSE, "Continuous", "Annual")</v>
+        <v>=QS.CONTEXT.ADD.ZERO.CURVE(History_Root2, "SOFR", History_Pillars, History_Rates2, "Actual365", "Continuous", "Annual", "Linear", FALSE)</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
     </row>
-    <row r="25" spans="1:4" ht="38" customHeight="1">
+    <row r="25" spans="1:4" ht="38.25" customHeight="1">
       <c r="A25" s="4" t="s">
         <v>94</v>
       </c>
@@ -2165,7 +2165,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="34" customHeight="1">
+    <row r="26" spans="1:4" ht="33.75" customHeight="1">
       <c r="A26" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B25),",",", ")</f>
         <v>=QS.CONTEXT.PREPARE("History.Context2", History_Root2, History_MarketInputs2)</v>
@@ -2173,7 +2173,7 @@
       <c r="B26" s="13"/>
       <c r="C26" s="13"/>
     </row>
-    <row r="28" spans="1:4" ht="38" customHeight="1">
+    <row r="28" spans="1:4" ht="38.25" customHeight="1">
       <c r="A28" s="4" t="s">
         <v>95</v>
       </c>
@@ -2185,7 +2185,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="34" customHeight="1">
+    <row r="29" spans="1:4" ht="33.75" customHeight="1">
       <c r="A29" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B28),",",", ")</f>
         <v>=QS.SNAPSHOT.FROM.CONTEXT("History.Snapshot2", History_Timestamp2, History_OriginalContext2)</v>
@@ -2228,7 +2228,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="38" customHeight="1">
+    <row r="35" spans="1:4" ht="38.25" customHeight="1">
       <c r="A35" s="4" t="s">
         <v>99</v>
       </c>
@@ -2240,7 +2240,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="34" customHeight="1">
+    <row r="36" spans="1:4" ht="33.75" customHeight="1">
       <c r="A36" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B35),",",", ")</f>
         <v>=QS.SNAPSHOT.FROM.RANGE("History.Archive", History_Snapshots, History_ObservationTimes)</v>
@@ -2288,7 +2288,7 @@
     <col min="2" max="3" width="48.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="38" customHeight="1">
+    <row r="1" spans="1:3" ht="38.25" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>101</v>
       </c>
@@ -2326,7 +2326,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="38" customHeight="1">
+    <row r="7" spans="1:3" ht="38.25" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>104</v>
       </c>
@@ -2346,7 +2346,7 @@
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
     </row>
-    <row r="10" spans="1:3" ht="38" customHeight="1">
+    <row r="10" spans="1:3" ht="38.25" customHeight="1">
       <c r="A10" s="4" t="s">
         <v>106</v>
       </c>
@@ -2358,7 +2358,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="34" customHeight="1">
+    <row r="11" spans="1:3" ht="33.75" customHeight="1">
       <c r="A11" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B10),",",", ")</f>
         <v>=QS.TRADE.CREATE("History.Trade", History_Instrument, History_TradeDate, History_Side)</v>
@@ -2366,7 +2366,7 @@
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
     </row>
-    <row r="13" spans="1:3" ht="38" customHeight="1">
+    <row r="13" spans="1:3" ht="38.25" customHeight="1">
       <c r="A13" s="4" t="s">
         <v>108</v>
       </c>
@@ -2378,7 +2378,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="34" customHeight="1">
+    <row r="14" spans="1:3" ht="33.75" customHeight="1">
       <c r="A14" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B13),",",", ")</f>
         <v>=QS.DISCOUNT.POLICY.CSA("History.Policy", "USD", "SOFR")</v>
@@ -2386,7 +2386,7 @@
       <c r="B14" s="13"/>
       <c r="C14" s="13"/>
     </row>
-    <row r="16" spans="1:3" ht="38" customHeight="1">
+    <row r="16" spans="1:3" ht="38.25" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>110</v>
       </c>
@@ -2398,7 +2398,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="34" customHeight="1">
+    <row r="17" spans="1:3" ht="33.75" customHeight="1">
       <c r="A17" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B16),",",", ")</f>
         <v>=QS.PRICER.CREATE("History.Pricer", "DiscountedCashflowPricer", History_Policy)</v>
@@ -2406,7 +2406,7 @@
       <c r="B17" s="13"/>
       <c r="C17" s="13"/>
     </row>
-    <row r="19" spans="1:3" ht="38" customHeight="1">
+    <row r="19" spans="1:3" ht="38.25" customHeight="1">
       <c r="A19" s="4" t="s">
         <v>112</v>
       </c>
@@ -2418,7 +2418,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="34" customHeight="1">
+    <row r="20" spans="1:3" ht="33.75" customHeight="1">
       <c r="A20" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B19),",",", ")</f>
         <v>=QS.SNAPSHOT.SELECTOR("History.Selector1", History_Query1, History_Rule1, "Mid")</v>
@@ -2426,7 +2426,7 @@
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
     </row>
-    <row r="22" spans="1:3" ht="38" customHeight="1">
+    <row r="22" spans="1:3" ht="38.25" customHeight="1">
       <c r="A22" s="4" t="s">
         <v>114</v>
       </c>
@@ -2438,7 +2438,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="34" customHeight="1">
+    <row r="23" spans="1:3" ht="33.75" customHeight="1">
       <c r="A23" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B22),",",", ")</f>
         <v>=QS.CONTEXT.FROM.SNAPSHOT("History.Selected1", History_Archive, History_Selector1)</v>
@@ -2446,7 +2446,7 @@
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
     </row>
-    <row r="25" spans="1:3" ht="38" customHeight="1">
+    <row r="25" spans="1:3" ht="38.25" customHeight="1">
       <c r="A25" s="4" t="s">
         <v>116</v>
       </c>
@@ -2458,7 +2458,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="34" customHeight="1">
+    <row r="26" spans="1:3" ht="33.75" customHeight="1">
       <c r="A26" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B25),",",", ")</f>
         <v>=QS.EVALUATE.RESULTS(History_Context1, History_Trade, "Value", , History_Pricer)</v>
@@ -2466,7 +2466,7 @@
       <c r="B26" s="13"/>
       <c r="C26" s="13"/>
     </row>
-    <row r="28" spans="1:3" ht="38" customHeight="1">
+    <row r="28" spans="1:3" ht="38.25" customHeight="1">
       <c r="A28" s="4" t="s">
         <v>118</v>
       </c>
@@ -2478,7 +2478,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="34" customHeight="1">
+    <row r="29" spans="1:3" ht="33.75" customHeight="1">
       <c r="A29" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B28),",",", ")</f>
         <v>=QS.SNAPSHOT.SELECTOR("History.Selector2", History_Query2, History_Rule2, "Mid")</v>
@@ -2486,7 +2486,7 @@
       <c r="B29" s="13"/>
       <c r="C29" s="13"/>
     </row>
-    <row r="31" spans="1:3" ht="38" customHeight="1">
+    <row r="31" spans="1:3" ht="38.25" customHeight="1">
       <c r="A31" s="4" t="s">
         <v>119</v>
       </c>
@@ -2498,7 +2498,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="34" customHeight="1">
+    <row r="32" spans="1:3" ht="33.75" customHeight="1">
       <c r="A32" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B31),",",", ")</f>
         <v>=QS.CONTEXT.FROM.SNAPSHOT("History.Selected2", History_Archive, History_Selector2)</v>
@@ -2506,7 +2506,7 @@
       <c r="B32" s="13"/>
       <c r="C32" s="13"/>
     </row>
-    <row r="34" spans="1:3" ht="38" customHeight="1">
+    <row r="34" spans="1:3" ht="38.25" customHeight="1">
       <c r="A34" s="4" t="s">
         <v>120</v>
       </c>
@@ -2518,7 +2518,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="34" customHeight="1">
+    <row r="35" spans="1:3" ht="33.75" customHeight="1">
       <c r="A35" s="13" t="str">
         <f>SUBSTITUTE(_xlfn.FORMULATEXT(B34),",",", ")</f>
         <v>=QS.EVALUATE.RESULTS(History_Context2, History_Trade, "Value", , History_Pricer)</v>
@@ -2567,7 +2567,7 @@
     <col min="2" max="3" width="36.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="38" customHeight="1">
+    <row r="1" spans="1:3" ht="38.25" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>121</v>
       </c>
